--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92538694468</v>
+        <v>46157.93112282862</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112282862</v>
+        <v>46157.93367385168</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93367385168</v>
+        <v>46157.93670356197</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93670356197</v>
+        <v>46158.28193372395</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28193372395</v>
+        <v>46158.29716449488</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29716449488</v>
+        <v>46158.29789235315</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29789235315</v>
+        <v>46158.33354996912</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33354996912</v>
+        <v>46158.3721013758</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3721013758</v>
+        <v>46158.37267225617</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
